--- a/survey_templates/034_tech_conference_attendee_satisfaction_poll--survey_templates.xlsx
+++ b/survey_templates/034_tech_conference_attendee_satisfaction_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,8 +704,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -733,12 +733,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_4}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 4}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_3}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 3}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied',_'value':_2}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied', 'value': 2}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_not_satisfied',_'value':_1}</t>
+          <t>very_not_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Not Satisfied', 'value': 1}</t>
+          <t>Very Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'technical',_'value':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Technical', 'value': 'technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'business',_'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Business', 'value': 'business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'social',_'value':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Social', 'value': 'social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_2}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 2}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_1}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 1}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
